--- a/equipment_request_forms/004_medical_equipment_loan_request_form--equipment_request_forms.xlsx
+++ b/equipment_request_forms/004_medical_equipment_loan_request_form--equipment_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'autoclave'}</t>
+          <t>autoclave</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Autoclave'}</t>
+          <t>Autoclave</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'defibrillator'}</t>
+          <t>defibrillator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Defibrillator'}</t>
+          <t>Defibrillator</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'ecg_machine'}</t>
+          <t>ecg_machine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'ECG Machine'}</t>
+          <t>ECG Machine</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'oxygen_tank'}</t>
+          <t>oxygen_tank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Oxygen Tank'}</t>
+          <t>Oxygen Tank</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'lab'}</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Lab'}</t>
+          <t>Lab</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'borrower'}</t>
+          <t>borrower</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Borrower'}</t>
+          <t>Borrower</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'loaner'}</t>
+          <t>loaner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Loaner'}</t>
+          <t>Loaner</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'On Time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'not_returned'}</t>
+          <t>not_returned</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Not Returned'}</t>
+          <t>Not Returned</t>
         </is>
       </c>
     </row>
